--- a/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
+++ b/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -469,15 +469,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Oportunidad</t>
         </is>
@@ -504,10 +509,10 @@
       <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -521,10 +526,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -536,44 +541,56 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6.25</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -583,56 +600,50 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5</v>
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -644,107 +655,107 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
+      <c r="F7" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -756,20 +767,26 @@
       <c r="D11" t="n">
         <v>6</v>
       </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="I11" t="n">
-        <v>5</v>
+      <c r="H11" t="n">
+        <v>6</v>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -781,16 +798,16 @@
       <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" t="n">
-        <v>8.5</v>
-      </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -804,240 +821,255 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.5</v>
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
         <v>7</v>
       </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>6.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>7.25</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>2.75</v>
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
+      <c r="F20" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.5</v>
+      <c r="K20" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -1050,84 +1082,81 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
+        <v>8.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1139,58 +1168,67 @@
       <c r="D25" t="n">
         <v>6</v>
       </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
       <c r="G25" t="n">
         <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
-      <c r="F26" t="n">
-        <v>2</v>
+      <c r="E26" t="n">
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
       </c>
       <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4.5</v>
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>4.5</v>
@@ -1199,408 +1237,396 @@
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.75</v>
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4.5</v>
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.25</v>
+        <v>6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Circuito eléctrico simple</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>4.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.5</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>7.25</v>
+        <v>4.5</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
       <c r="J32" t="n">
-        <v>0.75</v>
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D33" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.5</v>
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.5</v>
+        <v>6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>4.75</v>
+        <v>7.25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.25</v>
+        <v>8.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4</v>
-      </c>
-      <c r="I37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
+        <v>8.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1618,142 +1644,160 @@
       <c r="G42" t="n">
         <v>2</v>
       </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
       <c r="J42" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
         <v>6</v>
       </c>
-      <c r="F45" t="n">
-        <v>4.5</v>
-      </c>
       <c r="G45" t="n">
         <v>6</v>
       </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6</v>
+      </c>
       <c r="J45" t="n">
-        <v>-0.25</v>
+        <v>4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>-1</v>
+        <v>3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -1762,504 +1806,510 @@
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>3</v>
-      </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>6</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
-      </c>
-      <c r="I49" t="n">
-        <v>4</v>
-      </c>
-      <c r="J49" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Materiales opacos, transparentes y translúcidos</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" t="n">
-        <v>3</v>
-      </c>
-      <c r="I50" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-1</v>
+        <v>6</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Segunda ley de Newton</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
         <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
-      </c>
-      <c r="E51" t="n">
-        <v>6</v>
-      </c>
-      <c r="F51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>6</v>
       </c>
-      <c r="I51" t="n">
-        <v>9</v>
+      <c r="H51" t="n">
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>-1</v>
+        <v>4</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Energía potencial gravitatoria y elástica</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>7</v>
+        <v>5.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.5</v>
       </c>
       <c r="G52" t="n">
         <v>6</v>
       </c>
-      <c r="J52" t="n">
-        <v>-1.5</v>
+      <c r="H52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Expansión del universo y Big Bang</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C53" t="n">
-        <v>6.5</v>
+        <v>8.25</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" t="n">
-        <v>-1.5</v>
+        <v>8.25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Medición de magnitudes con instrumentos</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C54" t="n">
-        <v>3.5</v>
+        <v>8.25</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" t="n">
-        <v>2</v>
+        <v>8.25</v>
       </c>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" t="n">
-        <v>-1.5</v>
+        <v>8</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Energía cinética</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>6.75</v>
+        <v>2.5</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>6.5</v>
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.75</v>
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Conducción, convección y radiación</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>-2</v>
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Densidad</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>2.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
         <v>6</v>
       </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
       <c r="I57" t="n">
         <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>-2.5</v>
+        <v>3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Primera ley de Newton: inercia</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C58" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
         <v>9</v>
       </c>
-      <c r="F58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G58" t="n">
-        <v>6</v>
-      </c>
-      <c r="I58" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>-2.5</v>
+      <c r="H58" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Conservación de la energía mecánica</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
-      </c>
-      <c r="F59" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
         <v>7</v>
       </c>
-      <c r="I59" t="n">
-        <v>9</v>
-      </c>
-      <c r="J59" t="n">
-        <v>-3</v>
+      <c r="K59" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Formas de energía</t>
+          <t>Materiales opacos, transparentes y translúcidos</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
-      </c>
-      <c r="H60" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
       </c>
       <c r="J60" t="n">
-        <v>-3</v>
+        <v>3</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Movimiento, reposo y tipos de trayectoria</t>
+          <t>Segunda ley de Newton</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
         <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
-      </c>
-      <c r="I61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
-        <v>-3</v>
+        <v>9</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Transformaciones de la energía</t>
+          <t>Campo magnético y magnetismo terrestre</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G62" t="n">
         <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>6</v>
-      </c>
-      <c r="I62" t="n">
-        <v>5</v>
-      </c>
-      <c r="J62" t="n">
-        <v>-3</v>
+        <v>7</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Masa y peso</t>
+          <t>Circuito eléctrico simple</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>3.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.25</v>
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Color y dispersión de la luz</t>
+          <t>Conducción, convección y radiación</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -2267,123 +2317,547 @@
       <c r="G64" t="n">
         <v>6</v>
       </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>-4</v>
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tercera ley de Newton: acción y reacción</t>
+          <t>Expansión del universo y Big Bang</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>5</v>
       </c>
       <c r="C65" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D65" t="n">
         <v>9</v>
-      </c>
-      <c r="D65" t="n">
-        <v>7.5</v>
       </c>
       <c r="E65" t="n">
         <v>9</v>
       </c>
-      <c r="G65" t="n">
-        <v>6</v>
-      </c>
-      <c r="I65" t="n">
-        <v>9</v>
+      <c r="F65" t="n">
+        <v>6.5</v>
       </c>
       <c r="J65" t="n">
-        <v>-4</v>
+        <v>6</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Medición de magnitudes con instrumentos</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
         <v>6</v>
       </c>
-      <c r="H66" t="n">
-        <v>6</v>
-      </c>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.25</v>
+        <v>3</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rapidez y velocidad</t>
+          <t>Movimiento, reposo y tipos de trayectoria</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
         <v>6</v>
       </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6</v>
+      </c>
       <c r="J67" t="n">
-        <v>-4.25</v>
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Densidad</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Energía potencial gravitatoria y elástica</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5</v>
+      </c>
+      <c r="C69" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Magnitudes escalares y vectoriales</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Energía cinética</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Masa y peso</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Conservación de la energía mecánica</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7</v>
+      </c>
+      <c r="H73" t="n">
+        <v>8</v>
+      </c>
+      <c r="J73" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Formas de energía</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>6</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Primera ley de Newton: inercia</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Transformaciones de la energía</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Color y dispersión de la luz</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="J77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tercera ley de Newton: acción y reacción</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E78" t="n">
+        <v>9</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fuentes de energía renovables y no renovables</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6</v>
+      </c>
+      <c r="J79" t="n">
+        <v>9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Rapidez y velocidad</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>6</v>
+      </c>
+      <c r="H80" t="n">
+        <v>8</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Disipación de energía y eficiencia</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>2</v>
-      </c>
-      <c r="C68" t="n">
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" t="n">
         <v>7</v>
       </c>
-      <c r="D68" t="n">
-        <v>8</v>
-      </c>
-      <c r="E68" t="n">
-        <v>8</v>
-      </c>
-      <c r="F68" t="n">
-        <v>7</v>
-      </c>
-      <c r="I68" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>-5</v>
+      <c r="G81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>8</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-6</v>
       </c>
     </row>
   </sheetData>
@@ -2422,7 +2896,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTA(Oportunidad!A2:A68)</f>
+        <f>COUNTA(Oportunidad!A2:A81)</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2907,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Oportunidad!J2:J68,"&gt;=2")</f>
+        <f>COUNTIF(Oportunidad!K2:K81,"&gt;=2")</f>
         <v/>
       </c>
     </row>
@@ -2444,7 +2918,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Oportunidad!J2:J68,"&lt;=-2")</f>
+        <f>COUNTIF(Oportunidad!K2:K81,"&lt;=-2")</f>
         <v/>
       </c>
     </row>
@@ -2455,7 +2929,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>AVERAGE(Oportunidad!J2:J68)</f>
+        <f>AVERAGE(Oportunidad!K2:K81)</f>
         <v/>
       </c>
     </row>
@@ -2466,7 +2940,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -2476,7 +2950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">

--- a/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
+++ b/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
@@ -519,122 +519,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Calor como energía en tránsito</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Espejos planos e imágenes</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calor como energía en tránsito</t>
+          <t>Ley de gravitación universal</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Espejos planos e imágenes</t>
+          <t>Ventaja mecánica</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -643,213 +628,216 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ley de gravitación universal</t>
+          <t>Equilibrio térmico y ley cero</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ventaja mecánica</t>
+          <t>Ley de Ohm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Equilibrio térmico y ley cero</t>
+          <t>Lentes delgadas e imágenes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" t="n">
-        <v>4</v>
+      <c r="H9" t="n">
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ley de Ohm</t>
+          <t>Ondas electromagnéticas y espectro</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6.5</v>
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.5</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>7</v>
+      <c r="J10" t="n">
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
+        <v>6.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lentes delgadas e imágenes</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8.5</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ondas electromagnéticas y espectro</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -860,730 +848,745 @@
       <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>6</v>
       </c>
       <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
         <v>7</v>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>8.5</v>
+      <c r="E20" t="n">
+        <v>8</v>
       </c>
       <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="n">
         <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.5</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
       <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>6.5</v>
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
       </c>
-      <c r="H23" t="n">
-        <v>7</v>
+      <c r="J23" t="n">
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6</v>
+        <v>4.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.5</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="H25" t="n">
-        <v>6</v>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" t="n">
         <v>4.5</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="D28" t="n">
         <v>6</v>
       </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
       <c r="G28" t="n">
         <v>6</v>
       </c>
-      <c r="I28" t="n">
-        <v>6</v>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>7.75</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
+        <v>7.75</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
+        <v>8.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>4.25</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="J31" t="n">
-        <v>4</v>
-      </c>
       <c r="K31" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>4.5</v>
+        <v>7.25</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.5</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
-      <c r="H32" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
       <c r="K32" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D33" t="n">
-        <v>4.5</v>
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
       <c r="K33" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>7.75</v>
+        <v>2.5</v>
       </c>
       <c r="D34" t="n">
-        <v>7.75</v>
+        <v>2.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
-        <v>7.25</v>
+        <v>8.5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="F36" t="n">
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
+        <v>4.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
         <v>8.5</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="G38" t="n">
         <v>8.5</v>
       </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>4.75</v>
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1592,7 +1595,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1602,7 +1605,7 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1611,13 +1614,10 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>4</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1626,7 +1626,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1636,7 +1636,10 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -1647,8 +1650,8 @@
       <c r="H42" t="n">
         <v>2</v>
       </c>
-      <c r="J42" t="n">
-        <v>6</v>
+      <c r="I42" t="n">
+        <v>4</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -1657,29 +1660,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -1688,20 +1691,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -1709,11 +1712,11 @@
       <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -1722,29 +1725,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>3.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -1753,32 +1753,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" t="n">
         <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -1787,23 +1784,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>5</v>
@@ -1815,20 +1812,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
         <v>8.5</v>
@@ -1836,9 +1833,6 @@
       <c r="G48" t="n">
         <v>6</v>
       </c>
-      <c r="J48" t="n">
-        <v>6</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
@@ -1846,26 +1840,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -1874,26 +1868,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -1902,26 +1896,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>5.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.5</v>
       </c>
       <c r="G51" t="n">
         <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -1930,35 +1924,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>8.25</v>
       </c>
       <c r="D52" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4.5</v>
+        <v>8.25</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1983,60 +1974,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="D54" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
         <v>-0.5</v>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">

--- a/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
+++ b/asignaturas/fisica/brechas/Brechas_Fisica.xlsx
@@ -740,29 +740,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Carga eléctrica y electrización</t>
+          <t>Conservación de la energía</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6.5</v>
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -771,29 +771,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Conservación de la energía</t>
+          <t>Potencia eléctrica y efecto Joule</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -802,60 +799,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Potencia eléctrica y efecto Joule</t>
+          <t>Gas ideal y teoría cinética</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="H13" t="n">
-        <v>7</v>
-      </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gas ideal y teoría cinética</t>
+          <t>Corriente, voltaje y resistencia</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>7.25</v>
+        <v>3.5</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Corriente, voltaje y resistencia</t>
+          <t>Dilatación térmica</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -865,12 +859,18 @@
         <v>3.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
       <c r="K15" t="n">
@@ -880,29 +880,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dilatación térmica</t>
+          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
         <v>2.5</v>
@@ -911,23 +905,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fuerza magnética sobre corrientes y motor eléctrico</t>
+          <t>Ondas de radio y telecomunicaciones</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K17" t="n">
         <v>2.5</v>
@@ -936,32 +930,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ondas de radio y telecomunicaciones</t>
+          <t>Condiciones de equilibrio estático</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Condiciones de equilibrio estático</t>
+          <t>El sonido como onda mecánica</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -974,12 +971,15 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
         <v>6</v>
       </c>
       <c r="K19" t="n">
@@ -989,7 +989,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>El sonido como onda mecánica</t>
+          <t>Fuerza neta y diagrama de cuerpo libre</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1002,15 +1002,15 @@
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="n">
         <v>6</v>
       </c>
       <c r="K20" t="n">
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fuerza neta y diagrama de cuerpo libre</t>
+          <t>Fuerzas mecánicas comunes</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1032,16 +1032,10 @@
       <c r="D21" t="n">
         <v>6</v>
       </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>6</v>
       </c>
       <c r="K21" t="n">
@@ -1051,23 +1045,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fuerzas mecánicas comunes</t>
+          <t>Sistema Internacional de Unidades</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
-      <c r="I22" t="n">
-        <v>6</v>
+      <c r="J22" t="n">
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
@@ -1076,26 +1073,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sistema Internacional de Unidades</t>
+          <t>Trabajo mecánico</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
       </c>
+      <c r="H23" t="n">
+        <v>8</v>
+      </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
@@ -1104,66 +1101,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Trabajo mecánico</t>
+          <t>Flotación y hundimiento</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.5</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
       </c>
-      <c r="H24" t="n">
-        <v>8</v>
+      <c r="I24" t="n">
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Flotación y hundimiento</t>
+          <t>Electroimanes y efecto magnético de la corriente</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="D25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
       </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
       <c r="I25" t="n">
         <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Electroimanes y efecto magnético de la corriente</t>
+          <t>Presión</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1173,19 +1173,13 @@
         <v>4.5</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>1.5</v>
@@ -1194,23 +1188,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Refracción de la luz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D27" t="n">
-        <v>4.5</v>
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
       </c>
       <c r="K27" t="n">
         <v>1.5</v>
@@ -1219,82 +1219,79 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Refracción de la luz</t>
+          <t>Corriente alterna y transformador</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H28" t="n">
         <v>7</v>
       </c>
-      <c r="C28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
       <c r="K28" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Corriente alterna y transformador</t>
+          <t>Circuitos en serie y en paralelo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Circuitos en serie y en paralelo</t>
+          <t>Materiales magnéticos</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1303,76 +1300,85 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Materiales magnéticos</t>
+          <t>Longitud de onda, frecuencia y rapidez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>7.25</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Longitud de onda, frecuencia y rapidez</t>
+          <t>Gráficas del movimiento</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="D32" t="n">
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gráficas del movimiento</t>
+          <t>Imanes y polos magnéticos</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>2.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
       </c>
       <c r="K33" t="n">
         <v>0.5</v>
@@ -1381,23 +1387,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Imanes y polos magnéticos</t>
+          <t>Reflexión de la luz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1406,10 +1412,10 @@
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
         <v>0.5</v>
@@ -1418,35 +1424,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reflexión de la luz</t>
+          <t>Relaciones presión-volumen-temperatura en gases</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="K35" t="n">
         <v>0.5</v>
@@ -1455,73 +1449,82 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Relaciones presión-volumen-temperatura en gases</t>
+          <t>Posición, desplazamiento y trayectoria</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>8.5</v>
+        <v>4.75</v>
       </c>
       <c r="F36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G36" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Posición, desplazamiento y trayectoria</t>
+          <t>Absorción de radiación y efecto invernadero</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>4.75</v>
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.5</v>
       </c>
       <c r="F37" t="n">
         <v>4.5</v>
       </c>
+      <c r="G37" t="n">
+        <v>8.5</v>
+      </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Absorción de radiación y efecto invernadero</t>
+          <t>Calentamiento y enfriamiento</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>8.5</v>
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1530,7 +1533,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Calentamiento y enfriamiento</t>
+          <t>Características del sonido: tono, intensidad y eco</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1540,22 +1543,19 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>4</v>
+      <c r="J39" t="n">
+        <v>6</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Características del sonido: tono, intensidad y eco</t>
+          <t>El sonido se produce por vibraciones</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1576,6 +1576,9 @@
       <c r="D40" t="n">
         <v>2</v>
       </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
@@ -1584,9 +1587,6 @@
       </c>
       <c r="H40" t="n">
         <v>2</v>
-      </c>
-      <c r="J40" t="n">
-        <v>6</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>El sonido se produce por vibraciones</t>
+          <t>Fuentes de luz, propagación y sombras</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1605,10 +1605,10 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -1618,6 +1618,9 @@
       </c>
       <c r="H41" t="n">
         <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1626,31 +1629,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fuentes de luz, propagación y sombras</t>
+          <t>Fuerza elástica y ley de Hooke</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
       <c r="I42" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" t="n">
         <v>4</v>
       </c>
       <c r="K42" t="n">
@@ -1660,29 +1660,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fuerza elástica y ley de Hooke</t>
+          <t>Fuerzas de contacto y a distancia</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -1691,20 +1694,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fuerzas de contacto y a distancia</t>
+          <t>La energía y sus usos</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -1712,11 +1712,8 @@
       <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3</v>
+      <c r="H44" t="n">
+        <v>5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -1725,26 +1722,29 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>La energía y sus usos</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>3.5</v>
+        <v>5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>6</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -1753,29 +1753,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Máquinas simples</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
-      </c>
-      <c r="E46" t="n">
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -1784,26 +1781,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Máquinas simples</t>
+          <t>Ondas mecánicas transversales y longitudinales</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -1812,26 +1809,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ondas mecánicas transversales y longitudinales</t>
+          <t>Principio de Arquímedes: empuje</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>7</v>
       </c>
-      <c r="E48" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8.5</v>
-      </c>
       <c r="G48" t="n">
         <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -1840,26 +1837,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Principio de Arquímedes: empuje</t>
+          <t>Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
-      </c>
-      <c r="H49" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -1868,26 +1865,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Temperatura y escalas termométricas</t>
+          <t>Torque o momento de fuerza</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>5.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -1896,35 +1893,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Torque o momento de fuerza</t>
+          <t>Potencia mecánica</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>8.25</v>
       </c>
       <c r="D51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F51" t="n">
-        <v>4.5</v>
+        <v>8.25</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Potencia mecánica</t>
+          <t>Suma de vectores y componentes rectangulares</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1949,60 +1943,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Suma de vectores y componentes rectangulares</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
       </c>
       <c r="D53" t="n">
-        <v>8.25</v>
+        <v>2.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Conductores y aislantes eléctricos</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
         <v>-0.5</v>
@@ -2011,32 +2014,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Conductores y aislantes eléctricos</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D55" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
       </c>
       <c r="K55" t="n">
         <v>-0.5</v>
@@ -2045,7 +2051,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Fuerza como empuje o tirón</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2064,13 +2070,13 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
@@ -2082,35 +2088,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fuerza como empuje o tirón</t>
+          <t>Movimiento con aceleración constante</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
         <v>-0.5</v>
@@ -2119,23 +2113,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Movimiento con aceleración constante</t>
+          <t>Presión hidrostática y atmosférica</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>9</v>
+        <v>6.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
         <v>-0.5</v>
@@ -2144,26 +2138,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Presión hidrostática y atmosférica</t>
+          <t>Carga eléctrica y electrización</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
         <v>6.5</v>
       </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
       <c r="G59" t="n">
         <v>6</v>
       </c>
       <c r="H59" t="n">
         <v>7</v>
       </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
       <c r="K59" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
